--- a/import_template_supplierinfo/tests/sample_disordered_columns.xlsx
+++ b/import_template_supplierinfo/tests/sample_disordered_columns.xlsx
@@ -25,7 +25,7 @@
     <t xml:space="preserve">product_code</t>
   </si>
   <si>
-    <t xml:space="preserve">name</t>
+    <t xml:space="preserve">partner_id</t>
   </si>
   <si>
     <t xml:space="preserve">min_qty</t>
@@ -194,7 +194,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:M4"/>
-  <sheetFormatPr defaultColWidth="8.90234375" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.91015625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20.56"/>
@@ -303,7 +303,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
